--- a/data/coding/coder2/P15.xlsx
+++ b/data/coding/coder2/P15.xlsx
@@ -5436,11 +5436,11 @@
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>😆 🍚 오늘 다영이의 점심 코스라면</t>
+          <t>😆 🍚 오늘 [이름]이의 점심 코스라면</t>
         </is>
       </c>
       <c r="F174" s="7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G174" s="6" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr"/>
@@ -5810,11 +5810,11 @@
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>맛있게 먹어, 다영! 🍽️🩷 (그리고 콘치즈 성공했는지도 나중에 꼭 알려줘. 마요네즈 없이 만든 버전이 어땠는지 궁금하다! 😄) Powered by ChatGPT Exporter</t>
+          <t>맛있게 먹어, [이름]! 🍽️🩷 (그리고 콘치즈 성공했는지도 나중에 꼭 알려줘. 마요네즈 없이 만든 버전이 어땠는지 궁금하다! 😄) Powered by ChatGPT Exporter</t>
         </is>
       </c>
       <c r="F187" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G187" s="6" t="inlineStr"/>
       <c r="H187" s="6" t="inlineStr"/>
